--- a/data/b2_indio/B2 Índio 05-2026.xlsx
+++ b/data/b2_indio/B2 Índio 05-2026.xlsx
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>2078.53</v>
+        <v>1709.02</v>
       </c>
     </row>
     <row r="3">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>1458.19</v>
+        <v>1476.27</v>
       </c>
     </row>
     <row r="4">
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>51979.21</v>
+        <v>51416.37</v>
       </c>
     </row>
     <row r="5">
@@ -4855,16 +4855,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>1251.89</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="6">
@@ -4873,70 +4873,70 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>1702.98</v>
+        <v>3028.47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46152</v>
+        <v>46154</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>3900</v>
+        <v>2012.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46152</v>
+        <v>46155</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>3234.56</v>
+        <v>2724.22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1935.99</v>
+        <v>9533.799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -4945,88 +4945,88 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>9330.66</v>
+        <v>1706.42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46157</v>
+        <v>46159</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1573.52</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46159</v>
+        <v>46162</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3337.61</v>
+        <v>18196.91</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46162</v>
+        <v>46165</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>18169.92</v>
+        <v>1588.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>2988.41</v>
+        <v>1036.92</v>
       </c>
     </row>
     <row r="15">
@@ -5044,7 +5044,7 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>2987.08</v>
+        <v>3191.81</v>
       </c>
     </row>
     <row r="16">
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>1462.69</v>
+        <v>1974.44</v>
       </c>
     </row>
     <row r="17">
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3105.78</v>
+        <v>3284.26</v>
       </c>
     </row>
   </sheetData>
